--- a/reports/pdf_rolling5_20261022.xlsx
+++ b/reports/pdf_rolling5_20261022.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,470억   ·   현금 33억(0.7%)      오늘 2026-10-22  vs  5일전 2026-10-15      매수 17종목  /  매도 20종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,594억      오늘 2026-10-22  vs  5일전 2026-10-15      매수 17종목  /  매도 20종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>291</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2872293723</v>
+        <v>2878071885</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-346</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3563054504</v>
+        <v>-3570222262</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>142</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3634562901</v>
+        <v>3641874512</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-156</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2141434960</v>
+        <v>-2145742862</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>139</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>484272083</v>
+        <v>485246288</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-95</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2729028428</v>
+        <v>-2734518384</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3840818009</v>
+        <v>3848544541</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-53</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-943535114</v>
+        <v>-945433213</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>872951137</v>
+        <v>725366982</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.11%</t>
+          <t>0.87%→1.08%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>301→364</t>
+          <t>365→428</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -862,7 +862,7 @@
         <v>-35</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-899321970</v>
+        <v>-901131127</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -878,44 +878,44 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>723910699</v>
+        <v>874707243</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.87%→1.08%</t>
+          <t>1.00%→1.11%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>365→428</t>
+          <t>301→364</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-875316858</v>
+        <v>-1723677842</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.19%</t>
+          <t>2.12%→1.65%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>68→34</t>
+          <t>182→148</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
         <v>60</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2788171459</v>
+        <v>2793780393</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1720217300</v>
+        <v>-877077723</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.65%</t>
+          <t>0.40%→0.19%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>182→148</t>
+          <t>68→34</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         <v>44</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>946884895</v>
+        <v>948789733</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-899570471</v>
+        <v>-901380127</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2667698596</v>
+        <v>2673065176</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-247506129</v>
+        <v>-248004035</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>32</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1348659906</v>
+        <v>1351372990</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-722240778</v>
+        <v>-723693702</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2646923985</v>
+        <v>2652248773</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-13</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2061060078</v>
+        <v>-2065206290</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>453433217</v>
+        <v>454345384</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-438950630</v>
+        <v>-439833662</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2018914456</v>
+        <v>2022975884</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-912989478</v>
+        <v>-914826129</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>431197426</v>
+        <v>432064861</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-908615875</v>
+        <v>-910443728</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2147041123</v>
+        <v>2151360302</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-729198781</v>
+        <v>-459454865</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.01%</t>
+          <t>0.33%→0.26%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
         <v>6</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1574496824</v>
+        <v>1577664222</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-458532440</v>
+        <v>-1896384267</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.26%</t>
+          <t>2.92%→2.26%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>748482392</v>
+        <v>749988105</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-835656237</v>
+        <v>-837337318</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1411,23 +1411,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1892576990</v>
+        <v>-730665703</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.26%</t>
+          <t>1.34%→1.01%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1439,23 +1439,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-960204502</v>
+        <v>-732657703</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.74%</t>
+          <t>7.83%→7.23%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>184→180</t>
         </is>
       </c>
     </row>
@@ -1467,30 +1467,30 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-731186783</v>
+        <v>-962136135</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>7.83%→7.23%</t>
+          <t>0.91%→0.74%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>184→180</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억   ·   현금 59억(1.9%)      오늘 2026-10-22  vs  5일전 2026-10-15      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,216억      오늘 2026-10-22  vs  5일전 2026-10-15      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
         <v>56</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1453850147</v>
+        <v>1462048000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>-90</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-646380243</v>
+        <v>-650025000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>51</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1142257629</v>
+        <v>1148698500</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>-20</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-2808961056</v>
+        <v>-2824800000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>39</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>858967523</v>
+        <v>863811000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>-19</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-938022753</v>
+        <v>-943312000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>26</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>646646243</v>
+        <v>650292500</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>-17</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1787095072</v>
+        <v>-1797172000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>682449857</v>
+        <v>686298000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>-14</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2826517063</v>
+        <v>-2842455000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>638400240</v>
+        <v>642000000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>291323310</v>
+        <v>292966000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,290억   ·   현금 33억(1.4%)      오늘 2026-10-22  vs  5일전 2026-10-15      매수 12종목  /  매도 15종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,348억      오늘 2026-10-22  vs  5일전 2026-10-15      매수 12종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1951,7 +1951,7 @@
         <v>500</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>3140135858</v>
+        <v>3149665476</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>-113</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1155728156</v>
+        <v>-1159235535</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>300</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>4547101242</v>
+        <v>4560900690</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>-108</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2761474354</v>
+        <v>-2769854819</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>250</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>6935976894</v>
+        <v>6957026052</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-2138455584</v>
+        <v>-2144945324</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>152</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1433404472</v>
+        <v>1437754538</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-833635228</v>
+        <v>-2746455416</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>3.96%→3.08%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>150</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>6346171733</v>
+        <v>6365430963</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2141,23 +2141,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-2738145748</v>
+        <v>-836165126</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>3.96%→3.08%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         <v>100</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>2385580652</v>
+        <v>2392820362</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>-43</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-2366140146</v>
+        <v>-2373320859</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>85</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1170713820</v>
+        <v>1174266678</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2229,23 +2229,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-3165836865</v>
+        <v>-7191681088</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.02%→3.09%</t>
+          <t>5.01%→1.55%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>130→90</t>
+          <t>60→20</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
         <v>61</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>5065075383</v>
+        <v>5080446769</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2273,23 +2273,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-7169921958</v>
+        <v>-3175444480</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>5.01%→1.55%</t>
+          <t>5.02%→3.09%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>60→20</t>
+          <t>130→90</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <v>50</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2632705719</v>
+        <v>2640695400</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>-25</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-710072694</v>
+        <v>-712227608</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1817851997</v>
+        <v>1823368776</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>-24</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-3819565043</v>
+        <v>-3831156580</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>7</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>945665258</v>
+        <v>948535144</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>-16</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-4533921238</v>
+        <v>-4547680688</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>495436335</v>
+        <v>496939875</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2449,23 +2449,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>기가비스  (편출)</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1191999526</v>
+        <v>-1476013223</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.47%→0.00%</t>
+          <t>1.83%→1.18%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>14→0</t>
+          <t>40→26</t>
         </is>
       </c>
     </row>
@@ -2477,23 +2477,23 @@
       <c r="E53" s="17" t="n"/>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>기가비스  (편출)</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1471547402</v>
+        <v>-1195616981</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.83%→1.18%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>40→26</t>
+          <t>14→0</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>-8</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-623150570</v>
+        <v>-625041695</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>-7</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1725262471</v>
+        <v>-1730498262</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,073억   ·   현금 5억(0.2%)      오늘 2026-10-22  vs  5일전 2026-10-15      매수 3종목  /  매도 8종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,142억      오늘 2026-10-22  vs  5일전 2026-10-15      매수 3종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2652,7 +2652,7 @@
         <v>85</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>6584034351</v>
+        <v>6617624000</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>-311</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-5047158603</v>
+        <v>-5072907600</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>21</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>11664748166</v>
+        <v>11724258000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>-234</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-2109744753</v>
+        <v>-2120508000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>2082696744</v>
+        <v>2093322000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>-233</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-2292534419</v>
+        <v>-2304230200</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>-147</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-1310946468</v>
+        <v>-1317634500</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>-93</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-955147541</v>
+        <v>-960020400</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>-87</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-3645718902</v>
+        <v>-3664318200</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>-58</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-2109901554</v>
+        <v>-2120665600</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>-23</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-2163840773</v>
+        <v>-2174880000</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 269억   ·   현금 2억(0.9%)      오늘 2026-10-22  vs  5일전 2026-10-15      매수 8종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 258억      오늘 2026-10-22  vs  5일전 2026-10-15      매수 8종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B69" s="4" t="n"/>
@@ -3013,11 +3013,11 @@
         <v>61</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>105853332</v>
+        <v>99942400</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.40%</t>
+          <t>0.00%→0.39%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -3034,11 +3034,11 @@
         <v>-31</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-53171216</v>
+        <v>-51385600</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>3.10%→2.88%</t>
+          <t>3.12%→2.91%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -3057,11 +3057,11 @@
         <v>34</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>29887369</v>
+        <v>30333440</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.40%</t>
+          <t>0.31%→0.43%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -3078,7 +3078,7 @@
         <v>-22</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-47462814</v>
+        <v>-45478400</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
@@ -3101,11 +3101,11 @@
         <v>24</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>52742416</v>
+        <v>49612800</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>1.31%→1.50%</t>
+          <t>1.28%→1.47%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
@@ -3122,11 +3122,11 @@
         <v>-21</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-13577554</v>
+        <v>-12149760</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>7.65%→7.56%</t>
+          <t>7.14%→7.06%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -3145,11 +3145,11 @@
         <v>17</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>52849616</v>
+        <v>49232000</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.44%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -3166,11 +3166,11 @@
         <v>-20</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-51121015</v>
+        <v>-43520000</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>8.12%→7.89%</t>
+          <t>7.22%→7.02%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3189,11 +3189,11 @@
         <v>8</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>62872819</v>
+        <v>61491200</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>2.04%→2.27%</t>
+          <t>2.08%→2.31%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -3210,11 +3210,11 @@
         <v>-19</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-29024409</v>
+        <v>-27968000</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>4.89%→4.76%</t>
+          <t>4.92%→4.79%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3233,11 +3233,11 @@
         <v>7</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>36816511</v>
+        <v>37408000</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>1.15%→1.28%</t>
+          <t>1.22%→1.36%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3254,11 +3254,11 @@
         <v>-8</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-54886416</v>
+        <v>-57446400</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2.19%→1.98%</t>
+          <t>2.40%→2.16%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3277,11 +3277,11 @@
         <v>6</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>62953219</v>
+        <v>61248000</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>1.30%→1.53%</t>
+          <t>1.32%→1.56%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3298,11 +3298,11 @@
         <v>-6</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-48802815</v>
+        <v>-48115200</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>2.78%→2.59%</t>
+          <t>2.87%→2.66%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -3321,7 +3321,7 @@
         <v>6</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>23597407</v>
+        <v>22963200</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
@@ -3342,11 +3342,11 @@
         <v>-3</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>-8160602</v>
+        <v>-8313600</v>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>0.13%→0.10%</t>
+          <t>0.14%→0.11%</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -3392,7 +3392,7 @@
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 835억   ·   현금 3억(0.3%)      오늘 2026-10-22  vs  5일전 2026-10-15      매수 12종목  /  매도 14종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 863억      오늘 2026-10-22  vs  5일전 2026-10-15      매수 12종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B85" s="4" t="n"/>
@@ -3488,7 +3488,7 @@
         <v>962</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>2159843657</v>
+        <v>2173013700</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>-239</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-550703733</v>
+        <v>-554061750</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>257</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1159069859</v>
+        <v>1166137500</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>-187</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-834169498</v>
+        <v>-839256000</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>235</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>622035524</v>
+        <v>625828500</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>-133</v>
       </c>
       <c r="I90" s="15" t="n">
-        <v>-748151509</v>
+        <v>-752713500</v>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>141</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>598911527</v>
+        <v>602563500</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>-109</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-282440766</v>
+        <v>-284163000</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>96</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>664396719</v>
+        <v>668448000</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>-108</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-1452383823</v>
+        <v>-1461240000</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>85</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>504627938</v>
+        <v>507705000</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>-96</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-237734371</v>
+        <v>-239184000</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>74</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>351943957</v>
+        <v>354090000</v>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>-87</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-388802953</v>
+        <v>-391173750</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>59</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>420905949</v>
+        <v>423472500</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>-85</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-338741959</v>
+        <v>-340807500</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>46</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>231600772</v>
+        <v>233013000</v>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>-55</v>
       </c>
       <c r="I96" s="15" t="n">
-        <v>-276462966</v>
+        <v>-278148750</v>
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>30</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>255347969</v>
+        <v>256905000</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>-49</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-549662333</v>
+        <v>-553014000</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>21</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>232125572</v>
+        <v>233541000</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>-49</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-1012535877</v>
+        <v>-1018710000</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>15</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>308237962</v>
+        <v>310117500</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>-39</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>-468187143</v>
+        <v>-471042000</v>
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>-17</v>
       </c>
       <c r="I100" s="15" t="n">
-        <v>-181498778</v>
+        <v>-182605500</v>
       </c>
       <c r="J100" s="16" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>-4</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>-282079966</v>
+        <v>-283800000</v>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20261022.xlsx
+++ b/reports/pdf_rolling5_20261022.xlsx
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1723677842</v>
+        <v>-877077723</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.65%</t>
+          <t>0.40%→0.19%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>182→148</t>
+          <t>68→34</t>
         </is>
       </c>
     </row>
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-877077723</v>
+        <v>-1723677842</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.19%</t>
+          <t>2.12%→1.65%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>68→34</t>
+          <t>182→148</t>
         </is>
       </c>
     </row>
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-914826129</v>
+        <v>-910443728</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.26%</t>
+          <t>0.51%→0.34%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>25→14</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-910443728</v>
+        <v>-914826129</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.34%</t>
+          <t>0.45%→0.26%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>25→14</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1896384267</v>
+        <v>-837337318</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.26%</t>
+          <t>5.41%→4.54%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-837337318</v>
+        <v>-730665703</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>5.41%→4.54%</t>
+          <t>1.34%→1.01%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1411,23 +1411,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-730665703</v>
+        <v>-1896384267</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.01%</t>
+          <t>2.92%→2.26%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -2053,23 +2053,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-2144945324</v>
+        <v>-2746455416</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>3.96%→3.08%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2746455416</v>
+        <v>-2144945324</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>3.96%→3.08%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2229,23 +2229,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-7191681088</v>
+        <v>-3175444480</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.01%→1.55%</t>
+          <t>5.02%→3.09%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>60→20</t>
+          <t>130→90</t>
         </is>
       </c>
     </row>
@@ -2273,23 +2273,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-3175444480</v>
+        <v>-7191681088</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>5.02%→3.09%</t>
+          <t>5.01%→1.55%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>130→90</t>
+          <t>60→20</t>
         </is>
       </c>
     </row>
@@ -3898,23 +3898,23 @@
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-553014000</v>
+        <v>-1018710000</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>1.11%→0.50%</t>
+          <t>6.85%→5.46%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>87→38</t>
+          <t>275→226</t>
         </is>
       </c>
     </row>
@@ -3942,23 +3942,23 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-1018710000</v>
+        <v>-553014000</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>6.85%→5.46%</t>
+          <t>1.11%→0.50%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>275→226</t>
+          <t>87→38</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261022.xlsx
+++ b/reports/pdf_rolling5_20261022.xlsx
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-877077723</v>
+        <v>-1723677842</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.19%</t>
+          <t>2.12%→1.65%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>68→34</t>
+          <t>182→148</t>
         </is>
       </c>
     </row>
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1723677842</v>
+        <v>-877077723</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.65%</t>
+          <t>0.40%→0.19%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>182→148</t>
+          <t>68→34</t>
         </is>
       </c>
     </row>
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-910443728</v>
+        <v>-914826129</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.34%</t>
+          <t>0.45%→0.26%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>25→14</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-914826129</v>
+        <v>-910443728</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.26%</t>
+          <t>0.51%→0.34%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>25→14</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-459454865</v>
+        <v>-1896384267</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.26%</t>
+          <t>2.92%→2.26%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-837337318</v>
+        <v>-730665703</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>5.41%→4.54%</t>
+          <t>1.34%→1.01%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-730665703</v>
+        <v>-459454865</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.01%</t>
+          <t>0.33%→0.26%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1411,23 +1411,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1896384267</v>
+        <v>-837337318</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.26%</t>
+          <t>5.41%→4.54%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
@@ -1439,23 +1439,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-732657703</v>
+        <v>-962136135</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>7.83%→7.23%</t>
+          <t>0.91%→0.74%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>184→180</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1467,23 +1467,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-962136135</v>
+        <v>-732657703</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.74%</t>
+          <t>7.83%→7.23%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>184→180</t>
         </is>
       </c>
     </row>
@@ -2053,23 +2053,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-2746455416</v>
+        <v>-836165126</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>3.96%→3.08%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2141,23 +2141,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-836165126</v>
+        <v>-2746455416</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>3.96%→3.08%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2229,23 +2229,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-3175444480</v>
+        <v>-7191681088</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.02%→3.09%</t>
+          <t>5.01%→1.55%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>130→90</t>
+          <t>60→20</t>
         </is>
       </c>
     </row>
@@ -2273,23 +2273,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-7191681088</v>
+        <v>-3175444480</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>5.01%→1.55%</t>
+          <t>5.02%→3.09%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>60→20</t>
+          <t>130→90</t>
         </is>
       </c>
     </row>
@@ -3898,23 +3898,23 @@
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-1018710000</v>
+        <v>-553014000</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>6.85%→5.46%</t>
+          <t>1.11%→0.50%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>275→226</t>
+          <t>87→38</t>
         </is>
       </c>
     </row>
@@ -3942,23 +3942,23 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-553014000</v>
+        <v>-1018710000</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>1.11%→0.50%</t>
+          <t>6.85%→5.46%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>87→38</t>
+          <t>275→226</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261022.xlsx
+++ b/reports/pdf_rolling5_20261022.xlsx
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-914826129</v>
+        <v>-910443728</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.26%</t>
+          <t>0.51%→0.34%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>25→14</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-910443728</v>
+        <v>-914826129</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.34%</t>
+          <t>0.45%→0.26%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>25→14</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1896384267</v>
+        <v>-837337318</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.26%</t>
+          <t>5.41%→4.54%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-459454865</v>
+        <v>-1896384267</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.26%</t>
+          <t>2.92%→2.26%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1411,23 +1411,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-837337318</v>
+        <v>-459454865</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>5.41%→4.54%</t>
+          <t>0.33%→0.26%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1439,23 +1439,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-962136135</v>
+        <v>-732657703</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.74%</t>
+          <t>7.83%→7.23%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>184→180</t>
         </is>
       </c>
     </row>
@@ -1467,23 +1467,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-732657703</v>
+        <v>-962136135</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>7.83%→7.23%</t>
+          <t>0.91%→0.74%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>184→180</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -2053,23 +2053,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-836165126</v>
+        <v>-2746455416</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>3.96%→3.08%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2097,18 +2097,18 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2144945324</v>
+        <v>-836165126</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2141,23 +2141,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-2746455416</v>
+        <v>-2144945324</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>3.96%→3.08%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2229,23 +2229,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-7191681088</v>
+        <v>-3175444480</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.01%→1.55%</t>
+          <t>5.02%→3.09%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>60→20</t>
+          <t>130→90</t>
         </is>
       </c>
     </row>
@@ -2273,23 +2273,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-40</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-3175444480</v>
+        <v>-7191681088</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>5.02%→3.09%</t>
+          <t>5.01%→1.55%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>130→90</t>
+          <t>60→20</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261022.xlsx
+++ b/reports/pdf_rolling5_20261022.xlsx
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>725366982</v>
+        <v>874707243</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.87%→1.08%</t>
+          <t>1.00%→1.11%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>365→428</t>
+          <t>301→364</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -878,44 +878,44 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>874707243</v>
+        <v>725366982</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.11%</t>
+          <t>0.87%→1.08%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>301→364</t>
+          <t>365→428</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1723677842</v>
+        <v>-877077723</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.65%</t>
+          <t>0.40%→0.19%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>182→148</t>
+          <t>68→34</t>
         </is>
       </c>
     </row>
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-877077723</v>
+        <v>-1723677842</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.19%</t>
+          <t>2.12%→1.65%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>68→34</t>
+          <t>182→148</t>
         </is>
       </c>
     </row>
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-910443728</v>
+        <v>-914826129</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.34%</t>
+          <t>0.45%→0.26%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>25→14</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-914826129</v>
+        <v>-910443728</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.26%</t>
+          <t>0.51%→0.34%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>25→14</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-837337318</v>
+        <v>-730665703</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>5.41%→4.54%</t>
+          <t>1.34%→1.01%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-730665703</v>
+        <v>-459454865</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.01%</t>
+          <t>0.33%→0.26%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1896384267</v>
+        <v>-837337318</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.26%</t>
+          <t>5.41%→4.54%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
@@ -1411,23 +1411,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-459454865</v>
+        <v>-1896384267</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.26%</t>
+          <t>2.92%→2.26%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1439,23 +1439,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-732657703</v>
+        <v>-962136135</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>7.83%→7.23%</t>
+          <t>0.91%→0.74%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>184→180</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1467,23 +1467,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-962136135</v>
+        <v>-732657703</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.74%</t>
+          <t>7.83%→7.23%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>184→180</t>
         </is>
       </c>
     </row>
@@ -2053,23 +2053,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-2746455416</v>
+        <v>-2144945324</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>3.96%→3.08%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2141,23 +2141,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-2144945324</v>
+        <v>-2746455416</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>3.96%→3.08%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2449,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>기가비스  (편출)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1476013223</v>
+        <v>-1195616981</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.83%→1.18%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>40→26</t>
+          <t>14→0</t>
         </is>
       </c>
     </row>
@@ -2477,23 +2477,23 @@
       <c r="E53" s="17" t="n"/>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>기가비스  (편출)</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1195616981</v>
+        <v>-1476013223</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.47%→0.00%</t>
+          <t>1.83%→1.18%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>14→0</t>
+          <t>40→26</t>
         </is>
       </c>
     </row>
@@ -3898,23 +3898,23 @@
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-553014000</v>
+        <v>-1018710000</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>1.11%→0.50%</t>
+          <t>6.85%→5.46%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>87→38</t>
+          <t>275→226</t>
         </is>
       </c>
     </row>
@@ -3942,23 +3942,23 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-1018710000</v>
+        <v>-553014000</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>6.85%→5.46%</t>
+          <t>1.11%→0.50%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>275→226</t>
+          <t>87→38</t>
         </is>
       </c>
     </row>
